--- a/MULTILAYER/DADES_HCB/graph_metrics/multilayer/global_graph_metrics_MULTILAYER.xlsx
+++ b/MULTILAYER/DADES_HCB/graph_metrics/multilayer/global_graph_metrics_MULTILAYER.xlsx
@@ -462,16 +462,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9494597420704078</v>
+        <v>0.792784942488672</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4397870726146451</v>
+        <v>0.4702527947376042</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9747298710352039</v>
+        <v>0.896392471244336</v>
       </c>
       <c r="E2" t="n">
-        <v>1.050540257929592</v>
+        <v>1.207215057511328</v>
       </c>
     </row>
     <row r="3">
@@ -481,16 +481,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9375217845939352</v>
+        <v>0.793046357615894</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3686782256050352</v>
+        <v>0.4158810867148551</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9687608922969676</v>
+        <v>0.8965231788079471</v>
       </c>
       <c r="E3" t="n">
-        <v>1.062478215406065</v>
+        <v>1.206953642384106</v>
       </c>
     </row>
     <row r="4">
@@ -500,16 +500,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9498082955733705</v>
+        <v>0.7959219240153363</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4553787739373133</v>
+        <v>0.5260279919855745</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9749041477866852</v>
+        <v>0.8979609620076682</v>
       </c>
       <c r="E4" t="n">
-        <v>1.05019170442663</v>
+        <v>1.204078075984664</v>
       </c>
     </row>
     <row r="5">
@@ -519,16 +519,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9506796793307772</v>
+        <v>0.7964447542697805</v>
       </c>
       <c r="C5" t="n">
-        <v>0.489198737112472</v>
+        <v>0.5398243866970918</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9753398396653886</v>
+        <v>0.8982223771348902</v>
       </c>
       <c r="E5" t="n">
-        <v>1.049320320669223</v>
+        <v>1.20355524573022</v>
       </c>
     </row>
     <row r="6">
@@ -538,16 +538,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9489369118159637</v>
+        <v>0.796531892645521</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3975721853464171</v>
+        <v>0.4807558732931497</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9744684559079819</v>
+        <v>0.8982659463227606</v>
       </c>
       <c r="E6" t="n">
-        <v>1.051063088184036</v>
+        <v>1.203468107354479</v>
       </c>
     </row>
     <row r="7">
@@ -557,16 +557,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9500697107005925</v>
+        <v>0.7967933077727432</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4756921712624515</v>
+        <v>0.5460604584914635</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9750348553502963</v>
+        <v>0.8983966538863716</v>
       </c>
       <c r="E7" t="n">
-        <v>1.049930289299407</v>
+        <v>1.203206692227257</v>
       </c>
     </row>
     <row r="8">
@@ -576,16 +576,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9433600557685605</v>
+        <v>0.7941791565005228</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4452245088644332</v>
+        <v>0.5041022417417317</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9716800278842802</v>
+        <v>0.8970895782502614</v>
       </c>
       <c r="E8" t="n">
-        <v>1.05663994423144</v>
+        <v>1.205820843499477</v>
       </c>
     </row>
     <row r="9">
@@ -595,16 +595,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.945625653537818</v>
+        <v>0.7960962007668178</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4195949501499149</v>
+        <v>0.4714931261904592</v>
       </c>
       <c r="D9" t="n">
-        <v>0.972812826768909</v>
+        <v>0.8980481003834089</v>
       </c>
       <c r="E9" t="n">
-        <v>1.054374346462182</v>
+        <v>1.203903799233182</v>
       </c>
     </row>
     <row r="10">
@@ -614,16 +614,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9471941443011502</v>
+        <v>0.7975775531544091</v>
       </c>
       <c r="C10" t="n">
-        <v>0.4163475948177659</v>
+        <v>0.4988259936019613</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9735970721505751</v>
+        <v>0.8987887765772046</v>
       </c>
       <c r="E10" t="n">
-        <v>1.05280585569885</v>
+        <v>1.202422446845591</v>
       </c>
     </row>
     <row r="11">
@@ -633,16 +633,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9479783896828163</v>
+        <v>0.7960962007668178</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4715850308126482</v>
+        <v>0.5267664576157018</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9739891948414081</v>
+        <v>0.8980481003834089</v>
       </c>
       <c r="E11" t="n">
-        <v>1.052021610317184</v>
+        <v>1.203903799233182</v>
       </c>
     </row>
     <row r="12">
@@ -652,16 +652,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9490240501917044</v>
+        <v>0.7971418612757059</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4731667681434362</v>
+        <v>0.5298531915519584</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9745120250958522</v>
+        <v>0.8985709306378529</v>
       </c>
       <c r="E12" t="n">
-        <v>1.050975949808296</v>
+        <v>1.202858138724294</v>
       </c>
     </row>
     <row r="13">
@@ -671,16 +671,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9506796793307772</v>
+        <v>0.7974032764029279</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4916165624918766</v>
+        <v>0.5557197901729619</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9753398396653886</v>
+        <v>0.8987016382014639</v>
       </c>
       <c r="E13" t="n">
-        <v>1.049320320669223</v>
+        <v>1.202596723597072</v>
       </c>
     </row>
     <row r="14">
@@ -690,16 +690,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9293307772743116</v>
+        <v>0.7907807598466364</v>
       </c>
       <c r="C14" t="n">
-        <v>0.391178975349053</v>
+        <v>0.4270890352299105</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9646653886371558</v>
+        <v>0.8953903799233183</v>
       </c>
       <c r="E14" t="n">
-        <v>1.070669222725688</v>
+        <v>1.209219240153363</v>
       </c>
     </row>
     <row r="15">
@@ -709,16 +709,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9499825723248518</v>
+        <v>0.796009062391077</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5096898062818079</v>
+        <v>0.5560257287610507</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9749912861624259</v>
+        <v>0.8980045311955385</v>
       </c>
       <c r="E15" t="n">
-        <v>1.050017427675148</v>
+        <v>1.203990937608923</v>
       </c>
     </row>
     <row r="16">
@@ -728,16 +728,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9432729173928198</v>
+        <v>0.7897350993377483</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4084360876423341</v>
+        <v>0.4478734249444729</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9716364586964099</v>
+        <v>0.8948675496688742</v>
       </c>
       <c r="E16" t="n">
-        <v>1.05672708260718</v>
+        <v>1.210264900662252</v>
       </c>
     </row>
     <row r="17">
@@ -747,16 +747,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9495468804461484</v>
+        <v>0.796009062391077</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4828998610451594</v>
+        <v>0.5333357079958518</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9747734402230742</v>
+        <v>0.8980045311955385</v>
       </c>
       <c r="E17" t="n">
-        <v>1.050453119553852</v>
+        <v>1.203990937608923</v>
       </c>
     </row>
     <row r="18">
@@ -766,16 +766,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9416172882537469</v>
+        <v>0.7760543743464622</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4240098792763684</v>
+        <v>0.4529188047014177</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9708086441268735</v>
+        <v>0.888027187173231</v>
       </c>
       <c r="E18" t="n">
-        <v>1.058382711746253</v>
+        <v>1.223945625653538</v>
       </c>
     </row>
     <row r="19">
@@ -785,16 +785,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.945625653537818</v>
+        <v>0.7941791565005228</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4756640814016528</v>
+        <v>0.5231730440048054</v>
       </c>
       <c r="D19" t="n">
-        <v>0.972812826768909</v>
+        <v>0.8970895782502614</v>
       </c>
       <c r="E19" t="n">
-        <v>1.054374346462182</v>
+        <v>1.205820843499477</v>
       </c>
     </row>
     <row r="20">
@@ -804,16 +804,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9504182642035552</v>
+        <v>0.7950505402579295</v>
       </c>
       <c r="C20" t="n">
-        <v>0.419193725252029</v>
+        <v>0.4863355818374395</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9752091321017776</v>
+        <v>0.8975252701289648</v>
       </c>
       <c r="E20" t="n">
-        <v>1.049581735796445</v>
+        <v>1.20494945974207</v>
       </c>
     </row>
     <row r="21">
@@ -823,16 +823,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9469327291739282</v>
+        <v>0.7948762635064482</v>
       </c>
       <c r="C21" t="n">
-        <v>0.4016811193528194</v>
+        <v>0.4454844675799117</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9734663645869641</v>
+        <v>0.8974381317532241</v>
       </c>
       <c r="E21" t="n">
-        <v>1.053067270826072</v>
+        <v>1.205123736493552</v>
       </c>
     </row>
     <row r="22">
@@ -842,16 +842,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9512025095852213</v>
+        <v>0.786336702683862</v>
       </c>
       <c r="C22" t="n">
-        <v>0.5104938877364563</v>
+        <v>0.5147982382472859</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9756012547926106</v>
+        <v>0.893168351341931</v>
       </c>
       <c r="E22" t="n">
-        <v>1.048797490414779</v>
+        <v>1.213663297316138</v>
       </c>
     </row>
     <row r="23">
@@ -861,16 +861,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9396131056117114</v>
+        <v>0.786336702683862</v>
       </c>
       <c r="C23" t="n">
-        <v>0.4258344356061646</v>
+        <v>0.4775312073622281</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9698065528058557</v>
+        <v>0.893168351341931</v>
       </c>
       <c r="E23" t="n">
-        <v>1.060386894388289</v>
+        <v>1.213663297316138</v>
       </c>
     </row>
     <row r="24">
@@ -880,16 +880,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9499825723248518</v>
+        <v>0.7958347856395956</v>
       </c>
       <c r="C24" t="n">
-        <v>0.4990158033963416</v>
+        <v>0.5270896975633454</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9749912861624259</v>
+        <v>0.8979173928197979</v>
       </c>
       <c r="E24" t="n">
-        <v>1.050017427675148</v>
+        <v>1.204165214360404</v>
       </c>
     </row>
     <row r="25">
@@ -899,16 +899,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9507668177065179</v>
+        <v>0.7974032764029279</v>
       </c>
       <c r="C25" t="n">
-        <v>0.5156089347170711</v>
+        <v>0.5703213918897397</v>
       </c>
       <c r="D25" t="n">
-        <v>0.975383408853259</v>
+        <v>0.8987016382014639</v>
       </c>
       <c r="E25" t="n">
-        <v>1.049233182293482</v>
+        <v>1.202596723597072</v>
       </c>
     </row>
     <row r="26">
@@ -918,16 +918,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9489369118159637</v>
+        <v>0.7961833391425583</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4659303368815826</v>
+        <v>0.5296103604486762</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9744684559079819</v>
+        <v>0.8980916695712792</v>
       </c>
       <c r="E26" t="n">
-        <v>1.051063088184036</v>
+        <v>1.203816660857442</v>
       </c>
     </row>
     <row r="27">
@@ -937,16 +937,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.948588358313001</v>
+        <v>0.796270477518299</v>
       </c>
       <c r="C27" t="n">
-        <v>0.508322295969888</v>
+        <v>0.5477796545097975</v>
       </c>
       <c r="D27" t="n">
-        <v>0.9742941791565005</v>
+        <v>0.8981352387591496</v>
       </c>
       <c r="E27" t="n">
-        <v>1.051411641686999</v>
+        <v>1.203729522481701</v>
       </c>
     </row>
     <row r="28">
@@ -956,16 +956,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.9501568490763332</v>
+        <v>0.7970547228999652</v>
       </c>
       <c r="C28" t="n">
-        <v>0.4614255451793781</v>
+        <v>0.4890294537249467</v>
       </c>
       <c r="D28" t="n">
-        <v>0.9750784245381666</v>
+        <v>0.8985273614499826</v>
       </c>
       <c r="E28" t="n">
-        <v>1.049843150923667</v>
+        <v>1.202945277100035</v>
       </c>
     </row>
     <row r="29">
@@ -975,16 +975,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.9475426978041129</v>
+        <v>0.7956605088881143</v>
       </c>
       <c r="C29" t="n">
-        <v>0.5083495804888247</v>
+        <v>0.5549776278206144</v>
       </c>
       <c r="D29" t="n">
-        <v>0.9737713489020564</v>
+        <v>0.8978302544440572</v>
       </c>
       <c r="E29" t="n">
-        <v>1.052457302195887</v>
+        <v>1.204339491111886</v>
       </c>
     </row>
     <row r="30">
@@ -994,16 +994,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.9355176019518996</v>
+        <v>0.7877309166957128</v>
       </c>
       <c r="C30" t="n">
-        <v>0.3445907590183537</v>
+        <v>0.4169879177708864</v>
       </c>
       <c r="D30" t="n">
-        <v>0.9677588009759498</v>
+        <v>0.8938654583478564</v>
       </c>
       <c r="E30" t="n">
-        <v>1.0644823980481</v>
+        <v>1.212269083304287</v>
       </c>
     </row>
     <row r="31">
@@ -1013,16 +1013,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.9498082955733705</v>
+        <v>0.7967061693970025</v>
       </c>
       <c r="C31" t="n">
-        <v>0.4915868086848783</v>
+        <v>0.5650971692750999</v>
       </c>
       <c r="D31" t="n">
-        <v>0.9749041477866852</v>
+        <v>0.8983530846985012</v>
       </c>
       <c r="E31" t="n">
-        <v>1.05019170442663</v>
+        <v>1.203293830602998</v>
       </c>
     </row>
     <row r="32">
@@ -1032,16 +1032,16 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.9452771000348553</v>
+        <v>0.7944405716277448</v>
       </c>
       <c r="C32" t="n">
-        <v>0.3848066277745066</v>
+        <v>0.4659232257627305</v>
       </c>
       <c r="D32" t="n">
-        <v>0.9726385500174277</v>
+        <v>0.8972202858138725</v>
       </c>
       <c r="E32" t="n">
-        <v>1.054722899965145</v>
+        <v>1.205559428372255</v>
       </c>
     </row>
     <row r="33">
@@ -1051,16 +1051,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.9496340188218891</v>
+        <v>0.7956605088881143</v>
       </c>
       <c r="C33" t="n">
-        <v>0.4882472343453554</v>
+        <v>0.5495911215956902</v>
       </c>
       <c r="D33" t="n">
-        <v>0.9748170094109446</v>
+        <v>0.8978302544440572</v>
       </c>
       <c r="E33" t="n">
-        <v>1.050365981178111</v>
+        <v>1.204339491111886</v>
       </c>
     </row>
     <row r="34">
@@ -1070,16 +1070,16 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.9492854653189264</v>
+        <v>0.7958347856395956</v>
       </c>
       <c r="C34" t="n">
-        <v>0.4870223739433094</v>
+        <v>0.5330335713533367</v>
       </c>
       <c r="D34" t="n">
-        <v>0.9746427326594632</v>
+        <v>0.8979173928197979</v>
       </c>
       <c r="E34" t="n">
-        <v>1.050714534681074</v>
+        <v>1.204165214360404</v>
       </c>
     </row>
     <row r="35">
@@ -1089,16 +1089,16 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.9503311258278145</v>
+        <v>0.7974904147786686</v>
       </c>
       <c r="C35" t="n">
-        <v>0.5290744476606278</v>
+        <v>0.5858545834645961</v>
       </c>
       <c r="D35" t="n">
-        <v>0.9751655629139073</v>
+        <v>0.8987452073893343</v>
       </c>
       <c r="E35" t="n">
-        <v>1.049668874172185</v>
+        <v>1.202509585221331</v>
       </c>
     </row>
     <row r="36">
@@ -1108,16 +1108,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.9464098989194841</v>
+        <v>0.7929592192401533</v>
       </c>
       <c r="C36" t="n">
-        <v>0.4508364342947264</v>
+        <v>0.4984520497494894</v>
       </c>
       <c r="D36" t="n">
-        <v>0.9732049494597421</v>
+        <v>0.8964796096200767</v>
       </c>
       <c r="E36" t="n">
-        <v>1.053590101080516</v>
+        <v>1.207040780759847</v>
       </c>
     </row>
     <row r="37">
@@ -1127,16 +1127,16 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.9507668177065179</v>
+        <v>0.796009062391077</v>
       </c>
       <c r="C37" t="n">
-        <v>0.553246880595006</v>
+        <v>0.5693117628868005</v>
       </c>
       <c r="D37" t="n">
-        <v>0.975383408853259</v>
+        <v>0.8980045311955385</v>
       </c>
       <c r="E37" t="n">
-        <v>1.049233182293482</v>
+        <v>1.203990937608923</v>
       </c>
     </row>
     <row r="38">
@@ -1146,16 +1146,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.9465841756709655</v>
+        <v>0.7958347856395956</v>
       </c>
       <c r="C38" t="n">
-        <v>0.4639395907320151</v>
+        <v>0.5306194733141482</v>
       </c>
       <c r="D38" t="n">
-        <v>0.9732920878354827</v>
+        <v>0.8979173928197979</v>
       </c>
       <c r="E38" t="n">
-        <v>1.053415824329035</v>
+        <v>1.204165214360404</v>
       </c>
     </row>
     <row r="39">
@@ -1165,16 +1165,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.9464098989194841</v>
+        <v>0.7953119553851516</v>
       </c>
       <c r="C39" t="n">
-        <v>0.4601305684025016</v>
+        <v>0.5130676706923738</v>
       </c>
       <c r="D39" t="n">
-        <v>0.9732049494597421</v>
+        <v>0.8976559776925758</v>
       </c>
       <c r="E39" t="n">
-        <v>1.053590101080516</v>
+        <v>1.204688044614848</v>
       </c>
     </row>
     <row r="40">
@@ -1184,16 +1184,16 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.9499825723248518</v>
+        <v>0.7964447542697805</v>
       </c>
       <c r="C40" t="n">
-        <v>0.4924804467912139</v>
+        <v>0.5389276076785007</v>
       </c>
       <c r="D40" t="n">
-        <v>0.9749912861624259</v>
+        <v>0.8982223771348902</v>
       </c>
       <c r="E40" t="n">
-        <v>1.050017427675148</v>
+        <v>1.20355524573022</v>
       </c>
     </row>
     <row r="41">
@@ -1203,16 +1203,16 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.9470198675496688</v>
+        <v>0.7941791565005228</v>
       </c>
       <c r="C41" t="n">
-        <v>0.4229431755115071</v>
+        <v>0.4716282053818488</v>
       </c>
       <c r="D41" t="n">
-        <v>0.9735099337748344</v>
+        <v>0.8970895782502614</v>
       </c>
       <c r="E41" t="n">
-        <v>1.052980132450331</v>
+        <v>1.205820843499477</v>
       </c>
     </row>
     <row r="42">
@@ -1222,16 +1222,16 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.9476298361798536</v>
+        <v>0.7934820494945974</v>
       </c>
       <c r="C42" t="n">
-        <v>0.4473786460487389</v>
+        <v>0.4772238204741392</v>
       </c>
       <c r="D42" t="n">
-        <v>0.9738149180899268</v>
+        <v>0.8967410247472987</v>
       </c>
       <c r="E42" t="n">
-        <v>1.052370163820146</v>
+        <v>1.206517950505403</v>
       </c>
     </row>
     <row r="43">
@@ -1241,16 +1241,16 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.9491983269431857</v>
+        <v>0.7952248170094109</v>
       </c>
       <c r="C43" t="n">
-        <v>0.4672258170187639</v>
+        <v>0.524173059264799</v>
       </c>
       <c r="D43" t="n">
-        <v>0.9745991634715929</v>
+        <v>0.8976124085047055</v>
       </c>
       <c r="E43" t="n">
-        <v>1.050801673056814</v>
+        <v>1.204775182990589</v>
       </c>
     </row>
     <row r="44">
@@ -1260,16 +1260,16 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.9471941443011502</v>
+        <v>0.7942662948762635</v>
       </c>
       <c r="C44" t="n">
-        <v>0.4723302358371585</v>
+        <v>0.535358344607529</v>
       </c>
       <c r="D44" t="n">
-        <v>0.9735970721505751</v>
+        <v>0.8971331474381318</v>
       </c>
       <c r="E44" t="n">
-        <v>1.05280585569885</v>
+        <v>1.205733705123736</v>
       </c>
     </row>
     <row r="45">
@@ -1279,16 +1279,16 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.9489369118159637</v>
+        <v>0.7963576158940397</v>
       </c>
       <c r="C45" t="n">
-        <v>0.465896405612</v>
+        <v>0.5208390731283883</v>
       </c>
       <c r="D45" t="n">
-        <v>0.9744684559079819</v>
+        <v>0.8981788079470199</v>
       </c>
       <c r="E45" t="n">
-        <v>1.051063088184036</v>
+        <v>1.20364238410596</v>
       </c>
     </row>
     <row r="46">
@@ -1298,16 +1298,16 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.9491111885674451</v>
+        <v>0.7957476472638551</v>
       </c>
       <c r="C46" t="n">
-        <v>0.4906539540392238</v>
+        <v>0.5408467761751528</v>
       </c>
       <c r="D46" t="n">
-        <v>0.9745555942837225</v>
+        <v>0.8978738236319275</v>
       </c>
       <c r="E46" t="n">
-        <v>1.050888811432555</v>
+        <v>1.204252352736145</v>
       </c>
     </row>
     <row r="47">
@@ -1317,16 +1317,16 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.9498954339491111</v>
+        <v>0.7957476472638551</v>
       </c>
       <c r="C47" t="n">
-        <v>0.4638571896331082</v>
+        <v>0.5227776181867484</v>
       </c>
       <c r="D47" t="n">
-        <v>0.9749477169745556</v>
+        <v>0.8978738236319275</v>
       </c>
       <c r="E47" t="n">
-        <v>1.050104566050889</v>
+        <v>1.204252352736145</v>
       </c>
     </row>
     <row r="48">
@@ -1336,16 +1336,16 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.899355176019519</v>
+        <v>0.7705646566747996</v>
       </c>
       <c r="C48" t="n">
-        <v>0.3074151023694648</v>
+        <v>0.3485244940264506</v>
       </c>
       <c r="D48" t="n">
-        <v>0.9496775880097595</v>
+        <v>0.8852823283373998</v>
       </c>
       <c r="E48" t="n">
-        <v>1.100644823980481</v>
+        <v>1.2294353433252</v>
       </c>
     </row>
     <row r="49">
@@ -1355,16 +1355,16 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.9504182642035552</v>
+        <v>0.796009062391077</v>
       </c>
       <c r="C49" t="n">
-        <v>0.4415125714277557</v>
+        <v>0.5036763473355024</v>
       </c>
       <c r="D49" t="n">
-        <v>0.9752091321017776</v>
+        <v>0.8980045311955385</v>
       </c>
       <c r="E49" t="n">
-        <v>1.049581735796445</v>
+        <v>1.203990937608923</v>
       </c>
     </row>
     <row r="50">
@@ -1374,16 +1374,16 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.9503311258278145</v>
+        <v>0.7966190310212617</v>
       </c>
       <c r="C50" t="n">
-        <v>0.4734535665777501</v>
+        <v>0.5027406290856927</v>
       </c>
       <c r="D50" t="n">
-        <v>0.9751655629139073</v>
+        <v>0.8983095155106309</v>
       </c>
       <c r="E50" t="n">
-        <v>1.049668874172185</v>
+        <v>1.203380968978738</v>
       </c>
     </row>
     <row r="51">
@@ -1393,16 +1393,16 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.9420529801324503</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="C51" t="n">
-        <v>0.417292348976712</v>
+        <v>0.4980128218836917</v>
       </c>
       <c r="D51" t="n">
-        <v>0.9710264900662252</v>
+        <v>0.8947368421052632</v>
       </c>
       <c r="E51" t="n">
-        <v>1.05794701986755</v>
+        <v>1.210526315789474</v>
       </c>
     </row>
     <row r="52">
@@ -1412,16 +1412,16 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.9476298361798536</v>
+        <v>0.7967061693970025</v>
       </c>
       <c r="C52" t="n">
-        <v>0.414656568454447</v>
+        <v>0.4755451154939955</v>
       </c>
       <c r="D52" t="n">
-        <v>0.9738149180899268</v>
+        <v>0.8983530846985012</v>
       </c>
       <c r="E52" t="n">
-        <v>1.052370163820146</v>
+        <v>1.203293830602998</v>
       </c>
     </row>
     <row r="53">
@@ -1431,16 +1431,16 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.9481526664342976</v>
+        <v>0.7950505402579295</v>
       </c>
       <c r="C53" t="n">
-        <v>0.4693922834112378</v>
+        <v>0.5259108154925428</v>
       </c>
       <c r="D53" t="n">
-        <v>0.9740763332171488</v>
+        <v>0.8975252701289648</v>
       </c>
       <c r="E53" t="n">
-        <v>1.051847333565702</v>
+        <v>1.20494945974207</v>
       </c>
     </row>
     <row r="54">
@@ -1450,16 +1450,16 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.9510282328337399</v>
+        <v>0.7967061693970025</v>
       </c>
       <c r="C54" t="n">
-        <v>0.4880656999708419</v>
+        <v>0.5373179346375622</v>
       </c>
       <c r="D54" t="n">
-        <v>0.97551411641687</v>
+        <v>0.8983530846985012</v>
       </c>
       <c r="E54" t="n">
-        <v>1.04897176716626</v>
+        <v>1.203293830602998</v>
       </c>
     </row>
     <row r="55">
@@ -1469,16 +1469,16 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.9407459044963402</v>
+        <v>0.7482572324851865</v>
       </c>
       <c r="C55" t="n">
-        <v>0.4174408658938322</v>
+        <v>0.3446390282271105</v>
       </c>
       <c r="D55" t="n">
-        <v>0.9703729522481701</v>
+        <v>0.8741286162425932</v>
       </c>
       <c r="E55" t="n">
-        <v>1.05925409550366</v>
+        <v>1.251742767514814</v>
       </c>
     </row>
     <row r="56">
@@ -1488,16 +1488,16 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.9489369118159637</v>
+        <v>0.7947891251307075</v>
       </c>
       <c r="C56" t="n">
-        <v>0.5014190861489393</v>
+        <v>0.5256461213343773</v>
       </c>
       <c r="D56" t="n">
-        <v>0.9744684559079819</v>
+        <v>0.8973945625653538</v>
       </c>
       <c r="E56" t="n">
-        <v>1.051063088184036</v>
+        <v>1.205210874869292</v>
       </c>
     </row>
     <row r="57">
@@ -1507,16 +1507,16 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.9506796793307772</v>
+        <v>0.7942662948762635</v>
       </c>
       <c r="C57" t="n">
-        <v>0.5249337533897395</v>
+        <v>0.5681801142335082</v>
       </c>
       <c r="D57" t="n">
-        <v>0.9753398396653886</v>
+        <v>0.8971331474381318</v>
       </c>
       <c r="E57" t="n">
-        <v>1.049320320669223</v>
+        <v>1.205733705123736</v>
       </c>
     </row>
     <row r="58">
@@ -1526,16 +1526,16 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.9458870686650401</v>
+        <v>0.7897350993377483</v>
       </c>
       <c r="C58" t="n">
-        <v>0.4638540972429597</v>
+        <v>0.4813028856220147</v>
       </c>
       <c r="D58" t="n">
-        <v>0.97294353433252</v>
+        <v>0.8948675496688742</v>
       </c>
       <c r="E58" t="n">
-        <v>1.05411293133496</v>
+        <v>1.210264900662252</v>
       </c>
     </row>
     <row r="59">
@@ -1545,16 +1545,16 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.9513767863367026</v>
+        <v>0.7943534332520041</v>
       </c>
       <c r="C59" t="n">
-        <v>0.4371139930492967</v>
+        <v>0.4762601747551388</v>
       </c>
       <c r="D59" t="n">
-        <v>0.9756883931683513</v>
+        <v>0.8971767166260021</v>
       </c>
       <c r="E59" t="n">
-        <v>1.048623213663297</v>
+        <v>1.205646566747996</v>
       </c>
     </row>
     <row r="60">
@@ -1564,16 +1564,16 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.9501568490763332</v>
+        <v>0.790345067967933</v>
       </c>
       <c r="C60" t="n">
-        <v>0.4592728327912563</v>
+        <v>0.4842647438099319</v>
       </c>
       <c r="D60" t="n">
-        <v>0.9750784245381666</v>
+        <v>0.8951725339839666</v>
       </c>
       <c r="E60" t="n">
-        <v>1.049843150923667</v>
+        <v>1.209654932032067</v>
       </c>
     </row>
     <row r="61">
@@ -1583,16 +1583,16 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.9491983269431857</v>
+        <v>0.7909550365981178</v>
       </c>
       <c r="C61" t="n">
-        <v>0.4755818393178164</v>
+        <v>0.5332498544248342</v>
       </c>
       <c r="D61" t="n">
-        <v>0.9745991634715929</v>
+        <v>0.8954775182990589</v>
       </c>
       <c r="E61" t="n">
-        <v>1.050801673056814</v>
+        <v>1.209044963401882</v>
       </c>
     </row>
     <row r="62">
@@ -1602,16 +1602,16 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.9492854653189264</v>
+        <v>0.7941791565005228</v>
       </c>
       <c r="C62" t="n">
-        <v>0.427829822717904</v>
+        <v>0.4823039849151461</v>
       </c>
       <c r="D62" t="n">
-        <v>0.9746427326594632</v>
+        <v>0.8970895782502614</v>
       </c>
       <c r="E62" t="n">
-        <v>1.050714534681074</v>
+        <v>1.205820843499477</v>
       </c>
     </row>
     <row r="63">
@@ -1621,16 +1621,16 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.9516382014639247</v>
+        <v>0.7966190310212617</v>
       </c>
       <c r="C63" t="n">
-        <v>0.4661231898272918</v>
+        <v>0.5426830597504889</v>
       </c>
       <c r="D63" t="n">
-        <v>0.9758191007319623</v>
+        <v>0.8983095155106309</v>
       </c>
       <c r="E63" t="n">
-        <v>1.048361798536075</v>
+        <v>1.203380968978738</v>
       </c>
     </row>
     <row r="64">
@@ -1640,16 +1640,16 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.9500697107005925</v>
+        <v>0.7966190310212617</v>
       </c>
       <c r="C64" t="n">
-        <v>0.466109597707626</v>
+        <v>0.5225552605863054</v>
       </c>
       <c r="D64" t="n">
-        <v>0.9750348553502963</v>
+        <v>0.8983095155106309</v>
       </c>
       <c r="E64" t="n">
-        <v>1.049930289299407</v>
+        <v>1.203380968978738</v>
       </c>
     </row>
     <row r="65">
@@ -1659,16 +1659,16 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.9491983269431857</v>
+        <v>0.7957476472638551</v>
       </c>
       <c r="C65" t="n">
-        <v>0.4770899669526414</v>
+        <v>0.5345562935673259</v>
       </c>
       <c r="D65" t="n">
-        <v>0.9745991634715929</v>
+        <v>0.8978738236319275</v>
       </c>
       <c r="E65" t="n">
-        <v>1.050801673056814</v>
+        <v>1.204252352736145</v>
       </c>
     </row>
     <row r="66">
@@ -1678,16 +1678,16 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.9508539560822586</v>
+        <v>0.7966190310212617</v>
       </c>
       <c r="C66" t="n">
-        <v>0.4652918776624723</v>
+        <v>0.5117480829102444</v>
       </c>
       <c r="D66" t="n">
-        <v>0.9754269780411293</v>
+        <v>0.8983095155106309</v>
       </c>
       <c r="E66" t="n">
-        <v>1.049146043917741</v>
+        <v>1.203380968978738</v>
       </c>
     </row>
     <row r="67">
@@ -1697,16 +1697,16 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.92140118508191</v>
+        <v>0.7845067967933078</v>
       </c>
       <c r="C67" t="n">
-        <v>0.3235188887228813</v>
+        <v>0.3736021578968731</v>
       </c>
       <c r="D67" t="n">
-        <v>0.9607005925409551</v>
+        <v>0.8922533983966539</v>
       </c>
       <c r="E67" t="n">
-        <v>1.07859881491809</v>
+        <v>1.215493203206692</v>
       </c>
     </row>
     <row r="68">
@@ -1716,16 +1716,16 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.9500697107005925</v>
+        <v>0.7964447542697805</v>
       </c>
       <c r="C68" t="n">
-        <v>0.4333288508488705</v>
+        <v>0.4967995075430192</v>
       </c>
       <c r="D68" t="n">
-        <v>0.9750348553502963</v>
+        <v>0.8982223771348902</v>
       </c>
       <c r="E68" t="n">
-        <v>1.049930289299407</v>
+        <v>1.20355524573022</v>
       </c>
     </row>
     <row r="69">
@@ -1735,16 +1735,16 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.9457999302892994</v>
+        <v>0.7963576158940397</v>
       </c>
       <c r="C69" t="n">
-        <v>0.4086953848549643</v>
+        <v>0.4835993713754842</v>
       </c>
       <c r="D69" t="n">
-        <v>0.9728999651446497</v>
+        <v>0.8981788079470199</v>
       </c>
       <c r="E69" t="n">
-        <v>1.054200069710701</v>
+        <v>1.20364238410596</v>
       </c>
     </row>
     <row r="70">
@@ -1754,16 +1754,16 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.948326943185779</v>
+        <v>0.7947019867549668</v>
       </c>
       <c r="C70" t="n">
-        <v>0.4474976312970901</v>
+        <v>0.5011107138047594</v>
       </c>
       <c r="D70" t="n">
-        <v>0.9741634715928895</v>
+        <v>0.8973509933774835</v>
       </c>
       <c r="E70" t="n">
-        <v>1.051673056814221</v>
+        <v>1.205298013245033</v>
       </c>
     </row>
     <row r="71">
@@ -1773,16 +1773,16 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.9491111885674451</v>
+        <v>0.7906936214708958</v>
       </c>
       <c r="C71" t="n">
-        <v>0.4327867002722037</v>
+        <v>0.4619568548307575</v>
       </c>
       <c r="D71" t="n">
-        <v>0.9745555942837225</v>
+        <v>0.8953468107354479</v>
       </c>
       <c r="E71" t="n">
-        <v>1.050888811432555</v>
+        <v>1.209306378529104</v>
       </c>
     </row>
     <row r="72">
@@ -1792,16 +1792,16 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.9507668177065179</v>
+        <v>0.796270477518299</v>
       </c>
       <c r="C72" t="n">
-        <v>0.4292494313478296</v>
+        <v>0.4892441348736051</v>
       </c>
       <c r="D72" t="n">
-        <v>0.975383408853259</v>
+        <v>0.8981352387591496</v>
       </c>
       <c r="E72" t="n">
-        <v>1.049233182293482</v>
+        <v>1.203729522481701</v>
       </c>
     </row>
     <row r="73">
@@ -1811,16 +1811,16 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.9429243638898571</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="C73" t="n">
-        <v>0.388000263391574</v>
+        <v>0.4660773820470792</v>
       </c>
       <c r="D73" t="n">
-        <v>0.9714621819449285</v>
+        <v>0.8947368421052632</v>
       </c>
       <c r="E73" t="n">
-        <v>1.057075636110143</v>
+        <v>1.210526315789474</v>
       </c>
     </row>
     <row r="74">
@@ -1830,16 +1830,16 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.9517253398396653</v>
+        <v>0.796270477518299</v>
       </c>
       <c r="C74" t="n">
-        <v>0.3670005294018656</v>
+        <v>0.4299900591126266</v>
       </c>
       <c r="D74" t="n">
-        <v>0.9758626699198327</v>
+        <v>0.8981352387591496</v>
       </c>
       <c r="E74" t="n">
-        <v>1.048274660160335</v>
+        <v>1.203729522481701</v>
       </c>
     </row>
     <row r="75">
@@ -1849,16 +1849,16 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.9519867549668874</v>
+        <v>0.7968804461484837</v>
       </c>
       <c r="C75" t="n">
-        <v>0.5649089188227855</v>
+        <v>0.6015433145153203</v>
       </c>
       <c r="D75" t="n">
-        <v>0.9759933774834437</v>
+        <v>0.8984402230742419</v>
       </c>
       <c r="E75" t="n">
-        <v>1.048013245033113</v>
+        <v>1.203119553851516</v>
       </c>
     </row>
     <row r="76">
@@ -1868,16 +1868,16 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.948326943185779</v>
+        <v>0.7967061693970025</v>
       </c>
       <c r="C76" t="n">
-        <v>0.397881764108424</v>
+        <v>0.4682512955398557</v>
       </c>
       <c r="D76" t="n">
-        <v>0.9741634715928895</v>
+        <v>0.8983530846985012</v>
       </c>
       <c r="E76" t="n">
-        <v>1.051673056814221</v>
+        <v>1.203293830602998</v>
       </c>
     </row>
     <row r="77">
@@ -1887,16 +1887,16 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.9511153712094806</v>
+        <v>0.7967933077727432</v>
       </c>
       <c r="C77" t="n">
-        <v>0.4865189884511092</v>
+        <v>0.5465935901153237</v>
       </c>
       <c r="D77" t="n">
-        <v>0.9755576856047403</v>
+        <v>0.8983966538863716</v>
       </c>
       <c r="E77" t="n">
-        <v>1.048884628790519</v>
+        <v>1.203206692227257</v>
       </c>
     </row>
     <row r="78">
@@ -1906,16 +1906,16 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.9514639247124433</v>
+        <v>0.7969675845242244</v>
       </c>
       <c r="C78" t="n">
-        <v>0.4865265154575871</v>
+        <v>0.5340979817029859</v>
       </c>
       <c r="D78" t="n">
-        <v>0.9757319623562217</v>
+        <v>0.8984837922621123</v>
       </c>
       <c r="E78" t="n">
-        <v>1.048536075287557</v>
+        <v>1.203032415475775</v>
       </c>
     </row>
     <row r="79">
@@ -1925,16 +1925,16 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.9342976646915302</v>
+        <v>0.7794527710003486</v>
       </c>
       <c r="C79" t="n">
-        <v>0.3989391802366556</v>
+        <v>0.4247195012197626</v>
       </c>
       <c r="D79" t="n">
-        <v>0.9671488323457651</v>
+        <v>0.8897263855001742</v>
       </c>
       <c r="E79" t="n">
-        <v>1.06570233530847</v>
+        <v>1.220547228999652</v>
       </c>
     </row>
     <row r="80">
@@ -1944,16 +1944,16 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.9476298361798536</v>
+        <v>0.7926106657371906</v>
       </c>
       <c r="C80" t="n">
-        <v>0.390820754301893</v>
+        <v>0.4447000789399629</v>
       </c>
       <c r="D80" t="n">
-        <v>0.9738149180899268</v>
+        <v>0.8963053328685954</v>
       </c>
       <c r="E80" t="n">
-        <v>1.052370163820146</v>
+        <v>1.207389334262809</v>
       </c>
     </row>
     <row r="81">
@@ -1963,16 +1963,16 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.9513767863367026</v>
+        <v>0.7967061693970025</v>
       </c>
       <c r="C81" t="n">
-        <v>0.4969458355265638</v>
+        <v>0.5405477394504929</v>
       </c>
       <c r="D81" t="n">
-        <v>0.9756883931683513</v>
+        <v>0.8983530846985012</v>
       </c>
       <c r="E81" t="n">
-        <v>1.048623213663297</v>
+        <v>1.203293830602998</v>
       </c>
     </row>
     <row r="82">
@@ -1982,16 +1982,16 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.9508539560822586</v>
+        <v>0.7971418612757059</v>
       </c>
       <c r="C82" t="n">
-        <v>0.4856608620346541</v>
+        <v>0.5390072860729891</v>
       </c>
       <c r="D82" t="n">
-        <v>0.9754269780411293</v>
+        <v>0.8985709306378529</v>
       </c>
       <c r="E82" t="n">
-        <v>1.049146043917741</v>
+        <v>1.202858138724294</v>
       </c>
     </row>
     <row r="83">
@@ -2001,16 +2001,16 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.9505054025792959</v>
+        <v>0.7975775531544091</v>
       </c>
       <c r="C83" t="n">
-        <v>0.5226923876312616</v>
+        <v>0.5714686937129825</v>
       </c>
       <c r="D83" t="n">
-        <v>0.9752527012896479</v>
+        <v>0.8987887765772046</v>
       </c>
       <c r="E83" t="n">
-        <v>1.049494597420704</v>
+        <v>1.202422446845591</v>
       </c>
     </row>
     <row r="84">
@@ -2020,16 +2020,16 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.952073893342628</v>
+        <v>0.7969675845242244</v>
       </c>
       <c r="C84" t="n">
-        <v>0.472252630884207</v>
+        <v>0.5355980692007577</v>
       </c>
       <c r="D84" t="n">
-        <v>0.976036946671314</v>
+        <v>0.8984837922621123</v>
       </c>
       <c r="E84" t="n">
-        <v>1.047926106657372</v>
+        <v>1.203032415475775</v>
       </c>
     </row>
     <row r="85">
@@ -2039,16 +2039,16 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.9517253398396653</v>
+        <v>0.796009062391077</v>
       </c>
       <c r="C85" t="n">
-        <v>0.4347006531364088</v>
+        <v>0.4696996284403995</v>
       </c>
       <c r="D85" t="n">
-        <v>0.9758626699198327</v>
+        <v>0.8980045311955385</v>
       </c>
       <c r="E85" t="n">
-        <v>1.048274660160335</v>
+        <v>1.203990937608923</v>
       </c>
     </row>
     <row r="86">
@@ -2058,16 +2058,16 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.9492854653189264</v>
+        <v>0.7958347856395956</v>
       </c>
       <c r="C86" t="n">
-        <v>0.4532915371579802</v>
+        <v>0.5163925015144423</v>
       </c>
       <c r="D86" t="n">
-        <v>0.9746427326594632</v>
+        <v>0.8979173928197979</v>
       </c>
       <c r="E86" t="n">
-        <v>1.050714534681074</v>
+        <v>1.204165214360404</v>
       </c>
     </row>
     <row r="87">
@@ -2077,16 +2077,16 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.9452771000348553</v>
+        <v>0.793046357615894</v>
       </c>
       <c r="C87" t="n">
-        <v>0.4126453416820284</v>
+        <v>0.4500933965205758</v>
       </c>
       <c r="D87" t="n">
-        <v>0.9726385500174277</v>
+        <v>0.8965231788079471</v>
       </c>
       <c r="E87" t="n">
-        <v>1.054722899965145</v>
+        <v>1.206953642384106</v>
       </c>
     </row>
     <row r="88">
@@ -2096,16 +2096,16 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.9476298361798536</v>
+        <v>0.7935691878703381</v>
       </c>
       <c r="C88" t="n">
-        <v>0.4081294081322041</v>
+        <v>0.4311387323317126</v>
       </c>
       <c r="D88" t="n">
-        <v>0.9738149180899268</v>
+        <v>0.8967845939351691</v>
       </c>
       <c r="E88" t="n">
-        <v>1.052370163820146</v>
+        <v>1.206430812129662</v>
       </c>
     </row>
     <row r="89">
@@ -2115,16 +2115,16 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.9458870686650401</v>
+        <v>0.7960962007668178</v>
       </c>
       <c r="C89" t="n">
-        <v>0.4562017330236023</v>
+        <v>0.5165067732958615</v>
       </c>
       <c r="D89" t="n">
-        <v>0.97294353433252</v>
+        <v>0.8980481003834089</v>
       </c>
       <c r="E89" t="n">
-        <v>1.05411293133496</v>
+        <v>1.203903799233182</v>
       </c>
     </row>
     <row r="90">
@@ -2134,16 +2134,16 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.9474555594283722</v>
+        <v>0.7929592192401533</v>
       </c>
       <c r="C90" t="n">
-        <v>0.4368527843239333</v>
+        <v>0.4899436796242</v>
       </c>
       <c r="D90" t="n">
-        <v>0.9737277797141861</v>
+        <v>0.8964796096200767</v>
       </c>
       <c r="E90" t="n">
-        <v>1.052544440571628</v>
+        <v>1.207040780759847</v>
       </c>
     </row>
     <row r="91">
@@ -2153,16 +2153,16 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.9487626350644824</v>
+        <v>0.7727431160683165</v>
       </c>
       <c r="C91" t="n">
-        <v>0.4596750111675483</v>
+        <v>0.498863647840034</v>
       </c>
       <c r="D91" t="n">
-        <v>0.9743813175322412</v>
+        <v>0.8863715580341582</v>
       </c>
       <c r="E91" t="n">
-        <v>1.051237364935518</v>
+        <v>1.227256883931684</v>
       </c>
     </row>
     <row r="92">
@@ -2172,16 +2172,16 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.9479783896828163</v>
+        <v>0.7943534332520041</v>
       </c>
       <c r="C92" t="n">
-        <v>0.4344965589316534</v>
+        <v>0.492597781429381</v>
       </c>
       <c r="D92" t="n">
-        <v>0.9739891948414081</v>
+        <v>0.8971767166260021</v>
       </c>
       <c r="E92" t="n">
-        <v>1.052021610317184</v>
+        <v>1.205646566747996</v>
       </c>
     </row>
     <row r="93">
@@ -2191,16 +2191,16 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.9471941443011502</v>
+        <v>0.7937434646218194</v>
       </c>
       <c r="C93" t="n">
-        <v>0.4663660823906404</v>
+        <v>0.520133167135059</v>
       </c>
       <c r="D93" t="n">
-        <v>0.9735970721505751</v>
+        <v>0.8968717323109098</v>
       </c>
       <c r="E93" t="n">
-        <v>1.05280585569885</v>
+        <v>1.20625653537818</v>
       </c>
     </row>
     <row r="94">
@@ -2210,16 +2210,16 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.9495468804461484</v>
+        <v>0.7953990937608924</v>
       </c>
       <c r="C94" t="n">
-        <v>0.4857588590319654</v>
+        <v>0.5531894777417595</v>
       </c>
       <c r="D94" t="n">
-        <v>0.9747734402230742</v>
+        <v>0.8976995468804462</v>
       </c>
       <c r="E94" t="n">
-        <v>1.050453119553852</v>
+        <v>1.204600906239108</v>
       </c>
     </row>
     <row r="95">
@@ -2229,16 +2229,16 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.9491983269431857</v>
+        <v>0.796531892645521</v>
       </c>
       <c r="C95" t="n">
-        <v>0.5030335198401612</v>
+        <v>0.5530654905539201</v>
       </c>
       <c r="D95" t="n">
-        <v>0.9745991634715929</v>
+        <v>0.8982659463227606</v>
       </c>
       <c r="E95" t="n">
-        <v>1.050801673056814</v>
+        <v>1.203468107354479</v>
       </c>
     </row>
     <row r="96">
@@ -2248,16 +2248,16 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.9500697107005925</v>
+        <v>0.7937434646218194</v>
       </c>
       <c r="C96" t="n">
-        <v>0.4571666108180109</v>
+        <v>0.5114627775015246</v>
       </c>
       <c r="D96" t="n">
-        <v>0.9750348553502963</v>
+        <v>0.8968717323109098</v>
       </c>
       <c r="E96" t="n">
-        <v>1.049930289299407</v>
+        <v>1.20625653537818</v>
       </c>
     </row>
     <row r="97">
@@ -2267,16 +2267,16 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.9496340188218891</v>
+        <v>0.7943534332520041</v>
       </c>
       <c r="C97" t="n">
-        <v>0.486699396035995</v>
+        <v>0.5663745475314425</v>
       </c>
       <c r="D97" t="n">
-        <v>0.9748170094109446</v>
+        <v>0.8971767166260021</v>
       </c>
       <c r="E97" t="n">
-        <v>1.050365981178111</v>
+        <v>1.205646566747996</v>
       </c>
     </row>
     <row r="98">
@@ -2286,16 +2286,16 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.9504182642035552</v>
+        <v>0.793046357615894</v>
       </c>
       <c r="C98" t="n">
-        <v>0.4600944319022837</v>
+        <v>0.4817284023509047</v>
       </c>
       <c r="D98" t="n">
-        <v>0.9752091321017776</v>
+        <v>0.8965231788079471</v>
       </c>
       <c r="E98" t="n">
-        <v>1.049581735796445</v>
+        <v>1.206953642384106</v>
       </c>
     </row>
     <row r="99">
@@ -2305,16 +2305,16 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.9478041129313349</v>
+        <v>0.7938306029975601</v>
       </c>
       <c r="C99" t="n">
-        <v>0.4327921221142405</v>
+        <v>0.4666071070591896</v>
       </c>
       <c r="D99" t="n">
-        <v>0.9739020564656675</v>
+        <v>0.8969153014987801</v>
       </c>
       <c r="E99" t="n">
-        <v>1.052195887068665</v>
+        <v>1.20616939700244</v>
       </c>
     </row>
     <row r="100">
@@ -2324,16 +2324,16 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.9495468804461484</v>
+        <v>0.7948762635064482</v>
       </c>
       <c r="C100" t="n">
-        <v>0.4609815400161688</v>
+        <v>0.510469034282059</v>
       </c>
       <c r="D100" t="n">
-        <v>0.9747734402230742</v>
+        <v>0.8974381317532241</v>
       </c>
       <c r="E100" t="n">
-        <v>1.050453119553852</v>
+        <v>1.205123736493552</v>
       </c>
     </row>
     <row r="101">
@@ -2343,16 +2343,16 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.9363889857093064</v>
+        <v>0.7784942488672011</v>
       </c>
       <c r="C101" t="n">
-        <v>0.426644468122193</v>
+        <v>0.4242727010018321</v>
       </c>
       <c r="D101" t="n">
-        <v>0.9681944928546532</v>
+        <v>0.8892471244336005</v>
       </c>
       <c r="E101" t="n">
-        <v>1.063611014290694</v>
+        <v>1.221505751132799</v>
       </c>
     </row>
     <row r="102">
@@ -2362,16 +2362,16 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.9485012199372603</v>
+        <v>0.7956605088881143</v>
       </c>
       <c r="C102" t="n">
-        <v>0.4965208687202606</v>
+        <v>0.5456552878024176</v>
       </c>
       <c r="D102" t="n">
-        <v>0.9742506099686302</v>
+        <v>0.8978302544440572</v>
       </c>
       <c r="E102" t="n">
-        <v>1.05149878006274</v>
+        <v>1.204339491111886</v>
       </c>
     </row>
     <row r="103">
@@ -2381,16 +2381,16 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.9514639247124433</v>
+        <v>0.7968804461484837</v>
       </c>
       <c r="C103" t="n">
-        <v>0.5039097987114318</v>
+        <v>0.5499856096304557</v>
       </c>
       <c r="D103" t="n">
-        <v>0.9757319623562217</v>
+        <v>0.8984402230742419</v>
       </c>
       <c r="E103" t="n">
-        <v>1.048536075287557</v>
+        <v>1.203119553851516</v>
       </c>
     </row>
     <row r="104">
@@ -2400,16 +2400,16 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.948849773440223</v>
+        <v>0.7953119553851516</v>
       </c>
       <c r="C104" t="n">
-        <v>0.5174031035836673</v>
+        <v>0.5715021429319728</v>
       </c>
       <c r="D104" t="n">
-        <v>0.9744248867201115</v>
+        <v>0.8976559776925758</v>
       </c>
       <c r="E104" t="n">
-        <v>1.051150226559777</v>
+        <v>1.204688044614848</v>
       </c>
     </row>
     <row r="105">
@@ -2419,16 +2419,16 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.9289822237713489</v>
+        <v>0.7747472987103521</v>
       </c>
       <c r="C105" t="n">
-        <v>0.4152121142378946</v>
+        <v>0.4767170618517692</v>
       </c>
       <c r="D105" t="n">
-        <v>0.9644911118856745</v>
+        <v>0.887373649355176</v>
       </c>
       <c r="E105" t="n">
-        <v>1.071017776228651</v>
+        <v>1.225252701289648</v>
       </c>
     </row>
     <row r="106">
@@ -2438,16 +2438,16 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.9501568490763332</v>
+        <v>0.7956605088881143</v>
       </c>
       <c r="C106" t="n">
-        <v>0.4764715056216977</v>
+        <v>0.5145477170431131</v>
       </c>
       <c r="D106" t="n">
-        <v>0.9750784245381666</v>
+        <v>0.8978302544440572</v>
       </c>
       <c r="E106" t="n">
-        <v>1.049843150923667</v>
+        <v>1.204339491111886</v>
       </c>
     </row>
     <row r="107">
@@ -2457,16 +2457,16 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.9490240501917044</v>
+        <v>0.7959219240153363</v>
       </c>
       <c r="C107" t="n">
-        <v>0.4723977871202109</v>
+        <v>0.5253585846864312</v>
       </c>
       <c r="D107" t="n">
-        <v>0.9745120250958522</v>
+        <v>0.8979609620076682</v>
       </c>
       <c r="E107" t="n">
-        <v>1.050975949808296</v>
+        <v>1.204078075984664</v>
       </c>
     </row>
     <row r="108">
@@ -2476,16 +2476,16 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.8675496688741722</v>
+        <v>0.7429417915650053</v>
       </c>
       <c r="C108" t="n">
-        <v>0.359441177537945</v>
+        <v>0.3818096675297376</v>
       </c>
       <c r="D108" t="n">
-        <v>0.9337748344370861</v>
+        <v>0.8714708957825026</v>
       </c>
       <c r="E108" t="n">
-        <v>1.132450331125828</v>
+        <v>1.257058208434995</v>
       </c>
     </row>
     <row r="109">
@@ -2495,16 +2495,16 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.9504182642035552</v>
+        <v>0.7972289996514464</v>
       </c>
       <c r="C109" t="n">
-        <v>0.4880815695986339</v>
+        <v>0.5340195194113049</v>
       </c>
       <c r="D109" t="n">
-        <v>0.9752091321017776</v>
+        <v>0.8986144998257233</v>
       </c>
       <c r="E109" t="n">
-        <v>1.049581735796445</v>
+        <v>1.202771000348553</v>
       </c>
     </row>
     <row r="110">
@@ -2514,16 +2514,16 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.9420529801324503</v>
+        <v>0.7893865458347856</v>
       </c>
       <c r="C110" t="n">
-        <v>0.4487327738989039</v>
+        <v>0.5218281824111184</v>
       </c>
       <c r="D110" t="n">
-        <v>0.9710264900662252</v>
+        <v>0.8946932729173929</v>
       </c>
       <c r="E110" t="n">
-        <v>1.05794701986755</v>
+        <v>1.210613454165214</v>
       </c>
     </row>
     <row r="111">
@@ -2533,16 +2533,16 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.9491111885674451</v>
+        <v>0.7968804461484837</v>
       </c>
       <c r="C111" t="n">
-        <v>0.4513594167840662</v>
+        <v>0.5230207219382466</v>
       </c>
       <c r="D111" t="n">
-        <v>0.9745555942837225</v>
+        <v>0.8984402230742419</v>
       </c>
       <c r="E111" t="n">
-        <v>1.050888811432555</v>
+        <v>1.203119553851516</v>
       </c>
     </row>
     <row r="112">
@@ -2552,16 +2552,16 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.948588358313001</v>
+        <v>0.7940920181247821</v>
       </c>
       <c r="C112" t="n">
-        <v>0.4135379545735318</v>
+        <v>0.4750325263625397</v>
       </c>
       <c r="D112" t="n">
-        <v>0.9742941791565005</v>
+        <v>0.8970460090623911</v>
       </c>
       <c r="E112" t="n">
-        <v>1.051411641686999</v>
+        <v>1.205907981875218</v>
       </c>
     </row>
     <row r="113">
@@ -2571,16 +2571,16 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.9472812826768909</v>
+        <v>0.7928720808644127</v>
       </c>
       <c r="C113" t="n">
-        <v>0.4441754183117442</v>
+        <v>0.4933467037109665</v>
       </c>
       <c r="D113" t="n">
-        <v>0.9736406413384454</v>
+        <v>0.8964360404322064</v>
       </c>
       <c r="E113" t="n">
-        <v>1.052718717323109</v>
+        <v>1.207127919135587</v>
       </c>
     </row>
     <row r="114">
@@ -2590,16 +2590,16 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.948326943185779</v>
+        <v>0.7954862321366329</v>
       </c>
       <c r="C114" t="n">
-        <v>0.4727533281198266</v>
+        <v>0.5224998305721809</v>
       </c>
       <c r="D114" t="n">
-        <v>0.9741634715928895</v>
+        <v>0.8977431160683165</v>
       </c>
       <c r="E114" t="n">
-        <v>1.051673056814221</v>
+        <v>1.204513767863367</v>
       </c>
     </row>
     <row r="115">
@@ -2609,16 +2609,16 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.9398745207389334</v>
+        <v>0.7877309166957128</v>
       </c>
       <c r="C115" t="n">
-        <v>0.4078045437601281</v>
+        <v>0.4632052040847273</v>
       </c>
       <c r="D115" t="n">
-        <v>0.9699372603694667</v>
+        <v>0.8938654583478564</v>
       </c>
       <c r="E115" t="n">
-        <v>1.060125479261067</v>
+        <v>1.212269083304287</v>
       </c>
     </row>
     <row r="116">
@@ -2628,16 +2628,16 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.9495468804461484</v>
+        <v>0.7940920181247821</v>
       </c>
       <c r="C116" t="n">
-        <v>0.4585180227329572</v>
+        <v>0.4973411051465541</v>
       </c>
       <c r="D116" t="n">
-        <v>0.9747734402230742</v>
+        <v>0.8970460090623911</v>
       </c>
       <c r="E116" t="n">
-        <v>1.050453119553852</v>
+        <v>1.205907981875218</v>
       </c>
     </row>
     <row r="117">
@@ -2647,16 +2647,16 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.9502439874520739</v>
+        <v>0.7963576158940397</v>
       </c>
       <c r="C117" t="n">
-        <v>0.5128308794878493</v>
+        <v>0.5637590293329765</v>
       </c>
       <c r="D117" t="n">
-        <v>0.9751219937260369</v>
+        <v>0.8981788079470199</v>
       </c>
       <c r="E117" t="n">
-        <v>1.049756012547926</v>
+        <v>1.20364238410596</v>
       </c>
     </row>
     <row r="118">
@@ -2666,16 +2666,16 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.9471070059254095</v>
+        <v>0.793046357615894</v>
       </c>
       <c r="C118" t="n">
-        <v>0.4189712127563484</v>
+        <v>0.4685093776815268</v>
       </c>
       <c r="D118" t="n">
-        <v>0.9735535029627048</v>
+        <v>0.8965231788079471</v>
       </c>
       <c r="E118" t="n">
-        <v>1.05289299407459</v>
+        <v>1.206953642384106</v>
       </c>
     </row>
     <row r="119">
@@ -2685,16 +2685,16 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.9487626350644824</v>
+        <v>0.7877309166957128</v>
       </c>
       <c r="C119" t="n">
-        <v>0.4508747012581069</v>
+        <v>0.4536562211391731</v>
       </c>
       <c r="D119" t="n">
-        <v>0.9743813175322412</v>
+        <v>0.8938654583478564</v>
       </c>
       <c r="E119" t="n">
-        <v>1.051237364935518</v>
+        <v>1.212269083304287</v>
       </c>
     </row>
     <row r="120">
@@ -2704,16 +2704,16 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.9499825723248518</v>
+        <v>0.7958347856395956</v>
       </c>
       <c r="C120" t="n">
-        <v>0.4897360980408764</v>
+        <v>0.5387386090789619</v>
       </c>
       <c r="D120" t="n">
-        <v>0.9749912861624259</v>
+        <v>0.8979173928197979</v>
       </c>
       <c r="E120" t="n">
-        <v>1.050017427675148</v>
+        <v>1.204165214360404</v>
       </c>
     </row>
     <row r="121">
@@ -2723,16 +2723,16 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.9475426978041129</v>
+        <v>0.7964447542697805</v>
       </c>
       <c r="C121" t="n">
-        <v>0.3754033800682944</v>
+        <v>0.4448008649506593</v>
       </c>
       <c r="D121" t="n">
-        <v>0.9737713489020564</v>
+        <v>0.8982223771348902</v>
       </c>
       <c r="E121" t="n">
-        <v>1.052457302195887</v>
+        <v>1.20355524573022</v>
       </c>
     </row>
     <row r="122">
@@ -2742,16 +2742,16 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.9486754966887417</v>
+        <v>0.7922621122342279</v>
       </c>
       <c r="C122" t="n">
-        <v>0.4734933818619109</v>
+        <v>0.516597315213257</v>
       </c>
       <c r="D122" t="n">
-        <v>0.9743377483443708</v>
+        <v>0.896131056117114</v>
       </c>
       <c r="E122" t="n">
-        <v>1.051324503311258</v>
+        <v>1.207737887765772</v>
       </c>
     </row>
     <row r="123">
@@ -2761,16 +2761,16 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.9495468804461484</v>
+        <v>0.7960962007668178</v>
       </c>
       <c r="C123" t="n">
-        <v>0.4786971586159861</v>
+        <v>0.5298789660339284</v>
       </c>
       <c r="D123" t="n">
-        <v>0.9747734402230742</v>
+        <v>0.8980481003834089</v>
       </c>
       <c r="E123" t="n">
-        <v>1.050453119553852</v>
+        <v>1.203903799233182</v>
       </c>
     </row>
     <row r="124">
@@ -2780,16 +2780,16 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.9487626350644824</v>
+        <v>0.7951376786336702</v>
       </c>
       <c r="C124" t="n">
-        <v>0.4574926597390787</v>
+        <v>0.5020338140786494</v>
       </c>
       <c r="D124" t="n">
-        <v>0.9743813175322412</v>
+        <v>0.8975688393168352</v>
       </c>
       <c r="E124" t="n">
-        <v>1.051237364935518</v>
+        <v>1.20486232136633</v>
       </c>
     </row>
     <row r="125">
@@ -2799,16 +2799,16 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.9507668177065179</v>
+        <v>0.7972289996514464</v>
       </c>
       <c r="C125" t="n">
-        <v>0.4700191761790725</v>
+        <v>0.5260245237483083</v>
       </c>
       <c r="D125" t="n">
-        <v>0.975383408853259</v>
+        <v>0.8986144998257233</v>
       </c>
       <c r="E125" t="n">
-        <v>1.049233182293482</v>
+        <v>1.202771000348553</v>
       </c>
     </row>
     <row r="126">
@@ -2818,16 +2818,16 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.9510282328337399</v>
+        <v>0.7973161380271871</v>
       </c>
       <c r="C126" t="n">
-        <v>0.5197045334402373</v>
+        <v>0.5649184753629839</v>
       </c>
       <c r="D126" t="n">
-        <v>0.97551411641687</v>
+        <v>0.8986580690135936</v>
       </c>
       <c r="E126" t="n">
-        <v>1.04897176716626</v>
+        <v>1.202683861972813</v>
       </c>
     </row>
     <row r="127">
@@ -2837,16 +2837,16 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.9420529801324503</v>
+        <v>0.7961833391425583</v>
       </c>
       <c r="C127" t="n">
-        <v>0.3782549199135276</v>
+        <v>0.4600732120561416</v>
       </c>
       <c r="D127" t="n">
-        <v>0.9710264900662252</v>
+        <v>0.8980916695712792</v>
       </c>
       <c r="E127" t="n">
-        <v>1.05794701986755</v>
+        <v>1.203816660857442</v>
       </c>
     </row>
     <row r="128">
@@ -2856,16 +2856,16 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.9498082955733705</v>
+        <v>0.7971418612757059</v>
       </c>
       <c r="C128" t="n">
-        <v>0.4788168696795863</v>
+        <v>0.5472136874699179</v>
       </c>
       <c r="D128" t="n">
-        <v>0.9749041477866852</v>
+        <v>0.8985709306378529</v>
       </c>
       <c r="E128" t="n">
-        <v>1.05019170442663</v>
+        <v>1.202858138724294</v>
       </c>
     </row>
     <row r="129">
@@ -2875,16 +2875,16 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.9471941443011502</v>
+        <v>0.793307772743116</v>
       </c>
       <c r="C129" t="n">
-        <v>0.4267665353693154</v>
+        <v>0.4853399499548858</v>
       </c>
       <c r="D129" t="n">
-        <v>0.9735970721505751</v>
+        <v>0.8966538863715581</v>
       </c>
       <c r="E129" t="n">
-        <v>1.05280585569885</v>
+        <v>1.206692227256884</v>
       </c>
     </row>
     <row r="130">
@@ -2894,16 +2894,16 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.9442314395259672</v>
+        <v>0.7830254444057163</v>
       </c>
       <c r="C130" t="n">
-        <v>0.5230584932323132</v>
+        <v>0.5529479988423803</v>
       </c>
       <c r="D130" t="n">
-        <v>0.9721157197629836</v>
+        <v>0.8915127222028582</v>
       </c>
       <c r="E130" t="n">
-        <v>1.055768560474033</v>
+        <v>1.216974555594284</v>
       </c>
     </row>
     <row r="131">
@@ -2913,16 +2913,16 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.9505925409550366</v>
+        <v>0.7964447542697805</v>
       </c>
       <c r="C131" t="n">
-        <v>0.5076324503099152</v>
+        <v>0.5575648943865035</v>
       </c>
       <c r="D131" t="n">
-        <v>0.9752962704775183</v>
+        <v>0.8982223771348902</v>
       </c>
       <c r="E131" t="n">
-        <v>1.049407459044963</v>
+        <v>1.20355524573022</v>
       </c>
     </row>
     <row r="132">
@@ -2932,16 +2932,16 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.9448414081561519</v>
+        <v>0.7891251307075636</v>
       </c>
       <c r="C132" t="n">
-        <v>0.3964726289056648</v>
+        <v>0.4312525161155111</v>
       </c>
       <c r="D132" t="n">
-        <v>0.972420704078076</v>
+        <v>0.8945625653537818</v>
       </c>
       <c r="E132" t="n">
-        <v>1.055158591843848</v>
+        <v>1.210874869292436</v>
       </c>
     </row>
     <row r="133">
@@ -2951,16 +2951,16 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.9476298361798536</v>
+        <v>0.7947019867549668</v>
       </c>
       <c r="C133" t="n">
-        <v>0.4330452334556719</v>
+        <v>0.4967832414391514</v>
       </c>
       <c r="D133" t="n">
-        <v>0.9738149180899268</v>
+        <v>0.8973509933774835</v>
       </c>
       <c r="E133" t="n">
-        <v>1.052370163820146</v>
+        <v>1.205298013245033</v>
       </c>
     </row>
     <row r="134">
@@ -2970,16 +2970,16 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.9315963750435692</v>
+        <v>0.7772743116068317</v>
       </c>
       <c r="C134" t="n">
-        <v>0.3843078879793541</v>
+        <v>0.3933597180434148</v>
       </c>
       <c r="D134" t="n">
-        <v>0.9657981875217846</v>
+        <v>0.8886371558034158</v>
       </c>
       <c r="E134" t="n">
-        <v>1.068403624956431</v>
+        <v>1.222725688393168</v>
       </c>
     </row>
     <row r="135">
@@ -2989,16 +2989,16 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.9500697107005925</v>
+        <v>0.7968804461484837</v>
       </c>
       <c r="C135" t="n">
-        <v>0.513225594066631</v>
+        <v>0.5539243055049183</v>
       </c>
       <c r="D135" t="n">
-        <v>0.9750348553502963</v>
+        <v>0.8984402230742419</v>
       </c>
       <c r="E135" t="n">
-        <v>1.049930289299407</v>
+        <v>1.203119553851516</v>
       </c>
     </row>
     <row r="136">
@@ -3008,16 +3008,16 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.9447542697804113</v>
+        <v>0.7956605088881143</v>
       </c>
       <c r="C136" t="n">
-        <v>0.4514158040627187</v>
+        <v>0.5351659934793744</v>
       </c>
       <c r="D136" t="n">
-        <v>0.9723771348902056</v>
+        <v>0.8978302544440572</v>
       </c>
       <c r="E136" t="n">
-        <v>1.055245730219589</v>
+        <v>1.204339491111886</v>
       </c>
     </row>
     <row r="137">
@@ -3027,16 +3027,16 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.9485012199372603</v>
+        <v>0.7906936214708958</v>
       </c>
       <c r="C137" t="n">
-        <v>0.4579366072459711</v>
+        <v>0.4711129444842925</v>
       </c>
       <c r="D137" t="n">
-        <v>0.9742506099686302</v>
+        <v>0.8953468107354479</v>
       </c>
       <c r="E137" t="n">
-        <v>1.05149878006274</v>
+        <v>1.209306378529104</v>
       </c>
     </row>
     <row r="138">
@@ -3046,16 +3046,16 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.9498082955733705</v>
+        <v>0.7945277100034855</v>
       </c>
       <c r="C138" t="n">
-        <v>0.4779098226220708</v>
+        <v>0.5232007756961867</v>
       </c>
       <c r="D138" t="n">
-        <v>0.9749041477866852</v>
+        <v>0.8972638550017428</v>
       </c>
       <c r="E138" t="n">
-        <v>1.05019170442663</v>
+        <v>1.205472289996514</v>
       </c>
     </row>
     <row r="139">
@@ -3065,16 +3065,16 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.9447542697804113</v>
+        <v>0.7938306029975601</v>
       </c>
       <c r="C139" t="n">
-        <v>0.4142486039763699</v>
+        <v>0.4884007912506824</v>
       </c>
       <c r="D139" t="n">
-        <v>0.9723771348902056</v>
+        <v>0.8969153014987801</v>
       </c>
       <c r="E139" t="n">
-        <v>1.055245730219589</v>
+        <v>1.20616939700244</v>
       </c>
     </row>
     <row r="140">
@@ -3084,16 +3084,16 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.9393516904844894</v>
+        <v>0.7850296270477518</v>
       </c>
       <c r="C140" t="n">
-        <v>0.4504625733191063</v>
+        <v>0.4953684879207501</v>
       </c>
       <c r="D140" t="n">
-        <v>0.9696758452422447</v>
+        <v>0.892514813523876</v>
       </c>
       <c r="E140" t="n">
-        <v>1.060648309515511</v>
+        <v>1.214970372952248</v>
       </c>
     </row>
     <row r="141">
@@ -3103,16 +3103,16 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.948849773440223</v>
+        <v>0.7936563262460787</v>
       </c>
       <c r="C141" t="n">
-        <v>0.4575112078535158</v>
+        <v>0.5112281532140095</v>
       </c>
       <c r="D141" t="n">
-        <v>0.9744248867201115</v>
+        <v>0.8968281631230394</v>
       </c>
       <c r="E141" t="n">
-        <v>1.051150226559777</v>
+        <v>1.206343673753921</v>
       </c>
     </row>
     <row r="142">
@@ -3122,16 +3122,16 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.9303764377831997</v>
+        <v>0.7717845939351691</v>
       </c>
       <c r="C142" t="n">
-        <v>0.4382826361414743</v>
+        <v>0.4849145746554402</v>
       </c>
       <c r="D142" t="n">
-        <v>0.9651882188915999</v>
+        <v>0.8858922969675845</v>
       </c>
       <c r="E142" t="n">
-        <v>1.0696235622168</v>
+        <v>1.228215406064831</v>
       </c>
     </row>
     <row r="143">
@@ -3141,16 +3141,16 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.9509410944579993</v>
+        <v>0.7929592192401533</v>
       </c>
       <c r="C143" t="n">
-        <v>0.455262924312251</v>
+        <v>0.4930795803955921</v>
       </c>
       <c r="D143" t="n">
-        <v>0.9754705472289996</v>
+        <v>0.8964796096200767</v>
       </c>
       <c r="E143" t="n">
-        <v>1.049058905542001</v>
+        <v>1.207040780759847</v>
       </c>
     </row>
     <row r="144">
@@ -3160,16 +3160,16 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.9496340188218891</v>
+        <v>0.7940920181247821</v>
       </c>
       <c r="C144" t="n">
-        <v>0.4876174716151485</v>
+        <v>0.5372360031021179</v>
       </c>
       <c r="D144" t="n">
-        <v>0.9748170094109446</v>
+        <v>0.8970460090623911</v>
       </c>
       <c r="E144" t="n">
-        <v>1.050365981178111</v>
+        <v>1.205907981875218</v>
       </c>
     </row>
     <row r="145">
@@ -3179,16 +3179,16 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.9430115022655978</v>
+        <v>0.7885151620773789</v>
       </c>
       <c r="C145" t="n">
-        <v>0.4446278782293145</v>
+        <v>0.4478796378631056</v>
       </c>
       <c r="D145" t="n">
-        <v>0.9715057511327989</v>
+        <v>0.8942575810386895</v>
       </c>
       <c r="E145" t="n">
-        <v>1.056988497734402</v>
+        <v>1.211484837922621</v>
       </c>
     </row>
     <row r="146">
@@ -3198,16 +3198,16 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.9371732310909725</v>
+        <v>0.7879923318229348</v>
       </c>
       <c r="C146" t="n">
-        <v>0.422996644345859</v>
+        <v>0.4541229004610516</v>
       </c>
       <c r="D146" t="n">
-        <v>0.9685866155454862</v>
+        <v>0.8939961659114674</v>
       </c>
       <c r="E146" t="n">
-        <v>1.062826768909028</v>
+        <v>1.212007668177065</v>
       </c>
     </row>
     <row r="147">
@@ -3217,16 +3217,16 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.9491983269431857</v>
+        <v>0.7968804461484837</v>
       </c>
       <c r="C147" t="n">
-        <v>0.4619168022741897</v>
+        <v>0.5447659228238411</v>
       </c>
       <c r="D147" t="n">
-        <v>0.9745991634715929</v>
+        <v>0.8984402230742419</v>
       </c>
       <c r="E147" t="n">
-        <v>1.050801673056814</v>
+        <v>1.203119553851516</v>
       </c>
     </row>
     <row r="148">
@@ -3236,16 +3236,16 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.9500697107005925</v>
+        <v>0.7960962007668178</v>
       </c>
       <c r="C148" t="n">
-        <v>0.4859000526575007</v>
+        <v>0.5271711368807023</v>
       </c>
       <c r="D148" t="n">
-        <v>0.9750348553502963</v>
+        <v>0.8980481003834089</v>
       </c>
       <c r="E148" t="n">
-        <v>1.049930289299407</v>
+        <v>1.203903799233182</v>
       </c>
     </row>
     <row r="149">
@@ -3255,16 +3255,16 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.9491983269431857</v>
+        <v>0.7961833391425583</v>
       </c>
       <c r="C149" t="n">
-        <v>0.4256514661759097</v>
+        <v>0.4815366620012017</v>
       </c>
       <c r="D149" t="n">
-        <v>0.9745991634715929</v>
+        <v>0.8980916695712792</v>
       </c>
       <c r="E149" t="n">
-        <v>1.050801673056814</v>
+        <v>1.203816660857442</v>
       </c>
     </row>
     <row r="150">
@@ -3274,16 +3274,16 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.9479783896828163</v>
+        <v>0.7964447542697805</v>
       </c>
       <c r="C150" t="n">
-        <v>0.4606569165346928</v>
+        <v>0.519617871161836</v>
       </c>
       <c r="D150" t="n">
-        <v>0.9739891948414081</v>
+        <v>0.8982223771348902</v>
       </c>
       <c r="E150" t="n">
-        <v>1.052021610317184</v>
+        <v>1.20355524573022</v>
       </c>
     </row>
     <row r="151">
@@ -3293,16 +3293,16 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.9507668177065179</v>
+        <v>0.7949634018821889</v>
       </c>
       <c r="C151" t="n">
-        <v>0.5058991827515961</v>
+        <v>0.5401057023444773</v>
       </c>
       <c r="D151" t="n">
-        <v>0.975383408853259</v>
+        <v>0.8974817009410945</v>
       </c>
       <c r="E151" t="n">
-        <v>1.049233182293482</v>
+        <v>1.205036598117811</v>
       </c>
     </row>
     <row r="152">
@@ -3312,16 +3312,16 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.9498082955733705</v>
+        <v>0.796531892645521</v>
       </c>
       <c r="C152" t="n">
-        <v>0.4494560892643545</v>
+        <v>0.5176865379938368</v>
       </c>
       <c r="D152" t="n">
-        <v>0.9749041477866852</v>
+        <v>0.8982659463227606</v>
       </c>
       <c r="E152" t="n">
-        <v>1.05019170442663</v>
+        <v>1.203468107354479</v>
       </c>
     </row>
     <row r="153">
@@ -3331,16 +3331,16 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.9487626350644824</v>
+        <v>0.7958347856395956</v>
       </c>
       <c r="C153" t="n">
-        <v>0.4591475220928566</v>
+        <v>0.5311160466710377</v>
       </c>
       <c r="D153" t="n">
-        <v>0.9743813175322412</v>
+        <v>0.8979173928197979</v>
       </c>
       <c r="E153" t="n">
-        <v>1.051237364935518</v>
+        <v>1.204165214360404</v>
       </c>
     </row>
     <row r="154">
@@ -3350,16 +3350,16 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.9501568490763332</v>
+        <v>0.7961833391425583</v>
       </c>
       <c r="C154" t="n">
-        <v>0.4526694539047124</v>
+        <v>0.511609362157225</v>
       </c>
       <c r="D154" t="n">
-        <v>0.9750784245381666</v>
+        <v>0.8980916695712792</v>
       </c>
       <c r="E154" t="n">
-        <v>1.049843150923667</v>
+        <v>1.203816660857442</v>
       </c>
     </row>
     <row r="155">
@@ -3369,16 +3369,16 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.9486754966887417</v>
+        <v>0.7949634018821889</v>
       </c>
       <c r="C155" t="n">
-        <v>0.4233571632765398</v>
+        <v>0.4954795130520797</v>
       </c>
       <c r="D155" t="n">
-        <v>0.9743377483443708</v>
+        <v>0.8974817009410945</v>
       </c>
       <c r="E155" t="n">
-        <v>1.051324503311258</v>
+        <v>1.205036598117811</v>
       </c>
     </row>
     <row r="156">
@@ -3388,16 +3388,16 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.9475426978041129</v>
+        <v>0.7937434646218194</v>
       </c>
       <c r="C156" t="n">
-        <v>0.4145303785298705</v>
+        <v>0.4882941688698825</v>
       </c>
       <c r="D156" t="n">
-        <v>0.9737713489020564</v>
+        <v>0.8968717323109098</v>
       </c>
       <c r="E156" t="n">
-        <v>1.052457302195887</v>
+        <v>1.20625653537818</v>
       </c>
     </row>
   </sheetData>
